--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -501,7 +501,7 @@
     <t>FamilyMemberHistory.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|ActivityDefinition|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -535,7 +535,7 @@
     <t>FamilyMemberHistory.status</t>
   </si>
   <si>
-    <t>部分的|完了|エラーに入った|健康と知られていない / partial | completed | entered-in-error | health-unknown</t>
+    <t>部分的 | 完了 | エラー入力 | 不明 / partial | completed | entered-in-error | health-unknown</t>
   </si>
   <si>
     <t>特定の家族の家族歴史の記録のステータスを指定するコード。 / A code specifying the status of the record of the family history of a specific family member.</t>
@@ -581,7 +581,7 @@
     <t>家族の歴史が利用できない理由を説明するコード。 / Codes describing the reason why a family member's history is not available.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/history-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/history-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -696,7 +696,7 @@
     <t>出生登録に文書化された出生時に割り当てられた性別を説明するコード。 / Codes describing the sex assigned at birth as documented on the birth registration.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>FamilyMemberHistory.born[x]</t>
@@ -789,10 +789,10 @@
     <t>FamilyMemberHistory.reasonCode</t>
   </si>
   <si>
-    <t>なぜ家族の歴史が演奏されたのですか？ / Why was family member history performed?</t>
-  </si>
-  <si>
-    <t>家族の歴史がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
+    <t>家族歴が作成された理由 / Why was family member history performed?</t>
+  </si>
+  <si>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
   </si>
   <si>
     <t>テキストの理由は、ReasonCode.textを使用してキャプチャできます。 / Textual reasons can be captured using reasonCode.text.</t>
@@ -801,7 +801,7 @@
     <t>家族の歴史が行われた理由を示すコード。 / Codes indicating why the family member history was done.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t>この家族の歴史イベントを正当化する条件、観察、アレルギーへの耐性、またはアンケートのサンキアが示すことを示します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -915,7 +915,7 @@
     <t>状態または診断の識別。 / Identification of the Condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>.value</t>
@@ -933,7 +933,7 @@
     <t>患者の状態の結果。例えば死、永久障害、一時的な障害など。 / The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-outcome|4.0.1</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
@@ -1280,17 +1280,17 @@
   <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.2109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.2109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="253.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1299,26 +1299,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="147.171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.70703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="49.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="126.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="188.0234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -429,31 +429,55 @@
     <t>FamilyMemberHistory.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:siblingOrder</t>
+  </si>
+  <si>
+    <t>siblingOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
+</t>
+  </si>
+  <si>
+    <t>同胞内出生順</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory リソース全体に対して、関連する家族成員の同胞内出生順を表現する拡張。日本語での表現（長男、長女、次男など）を CodeableConcept で提供する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。家系図はスコープ外。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.modifierExtension</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -464,6 +488,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -877,6 +904,9 @@
   </si>
   <si>
     <t>FamilyMemberHistory.condition.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
   </si>
   <si>
     <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1277,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
@@ -2246,7 +2276,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2265,17 +2295,15 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2312,16 +2340,14 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2345,7 +2371,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2356,43 +2382,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2440,7 +2464,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2449,7 +2473,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2461,7 +2485,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2469,14 +2493,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2489,25 +2513,25 @@
         <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -2556,7 +2580,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2568,27 +2592,27 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2611,16 +2635,20 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>78</v>
       </c>
@@ -2668,7 +2696,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2683,24 +2711,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2723,17 +2751,15 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -2782,7 +2808,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2797,13 +2823,13 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -2811,10 +2837,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2822,31 +2848,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2872,13 +2898,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -2896,13 +2922,13 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
@@ -2917,18 +2943,18 @@
         <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2936,7 +2962,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
@@ -2945,24 +2971,24 @@
         <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2986,14 +3012,14 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
       </c>
@@ -3010,10 +3036,10 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>89</v>
@@ -3025,32 +3051,32 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -3065,16 +3091,18 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" s="2"/>
+      <c r="O16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3098,13 +3126,13 @@
         <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>78</v>
@@ -3122,10 +3150,10 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>89</v>
@@ -3137,16 +3165,16 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -3158,11 +3186,11 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3177,20 +3205,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>197</v>
-      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3241,7 +3265,7 @@
         <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3253,7 +3277,7 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
@@ -3301,9 +3325,11 @@
       <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3373,18 +3399,18 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3392,7 +3418,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3407,16 +3433,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3440,13 +3468,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3464,10 +3492,10 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3485,7 +3513,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3493,10 +3521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3504,7 +3532,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3519,20 +3547,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>216</v>
       </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3556,14 +3580,14 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3580,10 +3604,10 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -3601,7 +3625,7 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -3632,18 +3656,20 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>224</v>
       </c>
@@ -3670,13 +3696,13 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -3703,7 +3729,7 @@
         <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
@@ -3715,7 +3741,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -3723,10 +3749,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3746,20 +3772,18 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>231</v>
       </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>232</v>
       </c>
@@ -3810,7 +3834,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3819,7 +3843,7 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -3831,7 +3855,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -3839,10 +3863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3865,70 +3889,68 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="P23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="P23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="R23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3937,7 +3959,7 @@
         <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>101</v>
@@ -3949,7 +3971,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -3991,12 +4013,18 @@
       <c r="M24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4049,7 +4077,7 @@
         <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>101</v>
@@ -4061,7 +4089,7 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4069,10 +4097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4083,7 +4111,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4095,17 +4123,15 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4130,13 +4156,13 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -4154,13 +4180,13 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
@@ -4169,16 +4195,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
@@ -4209,15 +4235,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4242,13 +4270,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4281,24 +4309,24 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4318,16 +4346,16 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4378,7 +4406,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4393,24 +4421,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>78</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4433,13 +4461,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4490,7 +4518,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4505,13 +4533,13 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4519,10 +4547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4533,7 +4561,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -4545,13 +4573,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4608,13 +4636,13 @@
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -4623,7 +4651,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4631,21 +4659,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4657,17 +4685,15 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4716,19 +4742,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -4737,7 +4763,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -4745,14 +4771,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>280</v>
+        <v>148</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4765,26 +4791,24 @@
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -4832,7 +4856,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4853,7 +4877,7 @@
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>132</v>
+        <v>283</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -4861,42 +4885,46 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -4920,13 +4948,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -4944,19 +4972,19 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -4965,7 +4993,7 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>132</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -4973,10 +5001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4984,7 +5012,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -4999,13 +5027,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5032,34 +5060,34 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -5077,7 +5105,7 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5085,10 +5113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5111,13 +5139,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5144,13 +5172,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5168,7 +5196,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5189,7 +5217,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5197,10 +5225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5223,18 +5251,16 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5282,7 +5308,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5303,7 +5329,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5311,10 +5337,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5325,7 +5351,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5337,16 +5363,18 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5394,13 +5422,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5415,9 +5443,121 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -466,7 +466,7 @@
     <t>同胞内出生順</t>
   </si>
   <si>
-    <t>FamilyMemberHistory リソース全体に対して、関連する家族成員の同胞内出生順を表現する拡張。日本語での表現（長男、長女、次男など）を CodeableConcept で提供する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。家系図はスコープ外。</t>
+    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族成員の同胞内出生順を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生準名（長男、長女、次男、次女など）を CodeableConcept で表現する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。遺伝学的家系図はスコープ外。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -459,7 +459,7 @@
     <t>siblingOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
 </t>
   </si>
   <si>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory.xlsx
@@ -453,20 +453,20 @@
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.extension:siblingOrder</t>
-  </si>
-  <si>
-    <t>siblingOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder}
+    <t>FamilyMemberHistory.extension:genogramBasedSiblingOrder</t>
+  </si>
+  <si>
+    <t>genogramBasedSiblingOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_GenogramBasedSiblingOrder}
 </t>
   </si>
   <si>
     <t>同胞内出生順</t>
   </si>
   <si>
-    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族成員の同胞内出生順を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生準名（長男、長女、次男、次女など）を CodeableConcept で表現する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。遺伝学的家系図はスコープ外。</t>
+    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族成員の同胞内出生順を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生準名称（長男、長女、次男、次女など）を CodeableConcept で表現する。ジェノグラム（家族図）において社会学的・文化的文脈で利用される。また、臨床の現場で家族全員の生年月日や年齢を聴取できないが表現しておきたい場合も想定している。遺伝学的血統図を用途としておらず、その場合は、FamilyMemberHistory Geneticリソースや、GA4GH等のプロファイルを参照すること。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -1310,9 +1310,9 @@
   <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.55078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
